--- a/templates/tpl_booking_mssnhsmd6dzv.xlsx
+++ b/templates/tpl_booking_mssnhsmd6dzv.xlsx
@@ -2314,7 +2314,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3196,6 +3196,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4018,7 +4024,11 @@
       <c r="B3" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="89"/>
+      <c r="C3" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.name}}</t>
+        </is>
+      </c>
       <c r="D3" s="90"/>
       <c r="E3" s="90"/>
       <c r="F3" s="91"/>
@@ -4039,7 +4049,11 @@
       <c r="B4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="97"/>
+      <c r="C4" s="296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.address}}</t>
+        </is>
+      </c>
       <c r="D4" s="98"/>
       <c r="E4" s="98"/>
       <c r="F4" s="98"/>
@@ -4200,7 +4214,11 @@
       <c r="B13" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="89"/>
+      <c r="C13" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.name}}</t>
+        </is>
+      </c>
       <c r="D13" s="90"/>
       <c r="E13" s="90"/>
       <c r="F13" s="91"/>
@@ -4227,7 +4245,11 @@
       <c r="B14" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="97"/>
+      <c r="C14" s="296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.address}}</t>
+        </is>
+      </c>
       <c r="D14" s="98"/>
       <c r="E14" s="98"/>
       <c r="F14" s="98"/>
@@ -4455,7 +4477,11 @@
       <c r="B24" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="89"/>
+      <c r="C24" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{notify.name}}</t>
+        </is>
+      </c>
       <c r="D24" s="90"/>
       <c r="E24" s="90"/>
       <c r="F24" s="91"/>

--- a/templates/tpl_booking_mssnhsmd6dzv.xlsx
+++ b/templates/tpl_booking_mssnhsmd6dzv.xlsx
@@ -2314,7 +2314,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3196,6 +3196,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4013,7 +4016,11 @@
       <c r="L2" s="84"/>
       <c r="M2" s="84"/>
       <c r="N2" s="84"/>
-      <c r="O2" s="85"/>
+      <c r="O2" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.name}}</t>
+        </is>
+      </c>
       <c r="P2" s="86"/>
       <c r="Q2" s="86"/>
       <c r="R2" s="86"/>
@@ -4049,7 +4056,7 @@
       <c r="B4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="296" t="inlineStr">
+      <c r="C4" s="297" t="inlineStr">
         <is>
           <t xml:space="preserve">{{shipper.address}}</t>
         </is>
@@ -4207,7 +4214,11 @@
       <c r="L12" s="84"/>
       <c r="M12" s="84"/>
       <c r="N12" s="84"/>
-      <c r="O12" s="94"/>
+      <c r="O12" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.name}}</t>
+        </is>
+      </c>
       <c r="T12" s="95"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="2:20">
@@ -4245,7 +4256,7 @@
       <c r="B14" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="296" t="inlineStr">
+      <c r="C14" s="297" t="inlineStr">
         <is>
           <t xml:space="preserve">{{consignee.address}}</t>
         </is>
@@ -4466,7 +4477,11 @@
       <c r="L23" s="84"/>
       <c r="M23" s="84"/>
       <c r="N23" s="84"/>
-      <c r="O23" s="112"/>
+      <c r="O23" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{notify.name}}</t>
+        </is>
+      </c>
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -6118,7 +6133,7 @@
       <c r="T94" s="292"/>
     </row>
   </sheetData>
-  <mergeCells count="240">
+  <mergeCells count="242">
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="C3:L3"/>
@@ -6146,7 +6161,7 @@
     <mergeCell ref="E22:N22"/>
     <mergeCell ref="O22:T22"/>
     <mergeCell ref="B23:N23"/>
-    <mergeCell ref="O23:T23"/>
+    <mergeCell ref="O23:U23"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="O24:T24"/>
     <mergeCell ref="C25:N25"/>
@@ -6359,6 +6374,8 @@
     <mergeCell ref="J37:N38"/>
     <mergeCell ref="O16:T17"/>
     <mergeCell ref="O18:T19"/>
+    <mergeCell ref="O2:U2"/>
+    <mergeCell ref="O12:U12"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G57:L57">
